--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:25:56+00:00</t>
+    <t>2026-09-14T07:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:00:54+00:00</t>
+    <t>2026-09-14T09:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:05:35+00:00</t>
+    <t>2026-09-14T11:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:50:31+00:00</t>
+    <t>2026-09-15T06:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:30:22+00:00</t>
+    <t>2026-09-15T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:16:05+00:00</t>
+    <t>2026-09-16T05:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,13 +701,7 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-allergyintolerance-code</t>
   </si>
   <si>
     <t>substance/product:@@ -1052,6 +1046,9 @@
   </si>
   <si>
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
@@ -1582,7 +1579,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3664,13 +3661,11 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y19" s="2"/>
+      <c r="Z19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3703,21 +3698,21 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3740,13 +3735,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3797,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3812,7 +3807,7 @@
         <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3823,10 +3818,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3852,10 +3847,10 @@
         <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>154</v>
@@ -3899,7 +3894,7 @@
         <v>135</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
@@ -3908,7 +3903,7 @@
         <v>136</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3923,7 +3918,7 @@
         <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3934,10 +3929,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3945,10 +3940,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3960,19 +3955,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4021,7 +4016,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4036,21 +4031,21 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4073,19 +4068,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4134,7 +4129,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4149,25 +4144,25 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4186,13 +4181,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4243,7 +4238,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4258,21 +4253,21 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4295,13 +4290,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4352,7 +4347,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4367,10 +4362,10 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4378,10 +4373,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4404,13 +4399,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4461,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4476,10 +4471,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4487,10 +4482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4513,13 +4508,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4570,7 +4565,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4585,25 +4580,25 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4622,13 +4617,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4679,7 +4674,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4694,10 +4689,10 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4705,14 +4700,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4731,16 +4726,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4790,7 +4785,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4805,21 +4800,21 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4842,16 +4837,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4901,7 +4896,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4916,7 +4911,7 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
@@ -4927,10 +4922,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4953,16 +4948,16 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5012,7 +5007,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5027,7 +5022,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
@@ -5038,10 +5033,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5064,13 +5059,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5121,7 +5116,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5136,7 +5131,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
@@ -5147,10 +5142,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5173,13 +5168,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5230,7 +5225,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5245,7 +5240,7 @@
         <v>21</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
@@ -5256,10 +5251,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5337,7 +5332,7 @@
         <v>136</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5363,13 +5358,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5391,13 +5386,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5448,7 +5443,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5474,14 +5469,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5503,10 +5498,10 @@
         <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>154</v>
@@ -5561,7 +5556,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5587,10 +5582,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5616,13 +5611,13 @@
         <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5648,14 +5643,14 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5672,7 +5667,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5687,7 +5682,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5698,14 +5693,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5727,13 +5722,13 @@
         <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5759,14 +5754,14 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
       </c>
@@ -5783,7 +5778,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>87</v>
@@ -5804,19 +5799,19 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5835,16 +5830,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5894,7 +5889,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5909,7 +5904,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -5920,10 +5915,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5946,13 +5941,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6003,7 +5998,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6018,21 +6013,21 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6058,13 +6053,13 @@
         <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6093,11 +6088,11 @@
         <v>171</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6114,7 +6109,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6140,10 +6135,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6169,13 +6164,13 @@
         <v>167</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6201,14 +6196,14 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6225,7 +6220,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6240,7 +6235,7 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6251,10 +6246,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6277,16 +6272,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6336,7 +6331,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6351,7 +6346,7 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6362,10 +6357,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6388,13 +6383,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6445,7 +6440,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6460,7 +6455,7 @@
         <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6471,10 +6466,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6500,10 +6495,10 @@
         <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>154</v>
@@ -6547,7 +6542,7 @@
         <v>135</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
@@ -6556,7 +6551,7 @@
         <v>136</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6571,7 +6566,7 @@
         <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6582,10 +6577,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6608,16 +6603,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6667,7 +6662,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6682,7 +6677,7 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6693,10 +6688,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6719,13 +6714,13 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6776,7 +6771,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6791,7 +6786,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -6802,10 +6797,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6828,13 +6823,13 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6885,7 +6880,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>87</v>
@@ -6900,7 +6895,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:00:21+00:00</t>
+    <t>2026-09-30T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internen Dokumentationssystem.</t>
+    <t>External ids for this item</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -528,6 +528,10 @@
     <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -537,13 +541,244 @@
     <t>IAM-7</t>
   </si>
   <si>
-    <t>AllergyIntolerance.clinicalStatus</t>
+    <t>AllergyIntolerance.identifier:businessIdentifier</t>
+  </si>
+  <si>
+    <t>businessIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier innerhalb der e-Diagnose für einen Eintrag.</t>
+  </si>
+  <si>
+    <t>Dieser Identifier wird von der Fachanwendung e-Diagnose vergeben, sollte dieser durch den Client nicht gesetzt werden. Ein Client kann diesen Identifier nutzen, um einzelne Einträge im Zuge einer Bearbeitung miteinander zu verknüpfen.</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.use</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.type</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.system</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/CodeSystem/at-ediag-codesystem-business-identifier</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.value</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.period</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.clinicalStatus</t>
+  </si>
+  <si>
     <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
   </si>
   <si>
@@ -552,9 +787,6 @@
   <si>
     <t>Refer to [discussion](http://hl7.org/fhir/R4/extensibility.html#Special-Case) if clincalStatus is missing data.
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergyintolerance-clinical|4.0.1</t>
@@ -726,35 +958,7 @@
     <t>AllergyIntolerance.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AllergyIntolerance.code.coding</t>
@@ -1551,12 +1755,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM48"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.27734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.9609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1573,7 +1777,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
@@ -3007,16 +3211,14 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>157</v>
@@ -3034,55 +3236,59 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3106,13 +3312,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3130,36 +3336,36 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3167,32 +3373,30 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3217,13 +3421,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3250,16 +3454,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3267,21 +3471,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3290,19 +3494,19 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3328,28 +3532,28 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>183</v>
@@ -3358,47 +3562,47 @@
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>88</v>
@@ -3407,15 +3611,17 @@
         <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3439,13 +3645,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3469,7 +3675,7 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
@@ -3478,32 +3684,32 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3515,18 +3721,20 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3550,13 +3758,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3574,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3589,25 +3797,25 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3617,7 +3825,7 @@
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -3626,18 +3834,20 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3646,10 +3856,10 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3661,11 +3871,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3683,7 +3895,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3698,21 +3910,21 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3720,7 +3932,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>87</v>
@@ -3732,18 +3944,20 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3756,7 +3970,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -3792,7 +4006,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3804,16 +4018,16 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3821,18 +4035,18 @@
         <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3841,20 +4055,18 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3891,48 +4103,48 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3943,7 +4155,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3955,20 +4167,18 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4016,13 +4226,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4031,21 +4241,21 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4053,35 +4263,33 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4105,13 +4313,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4129,7 +4337,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4138,31 +4346,31 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4175,21 +4383,23 @@
         <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4214,13 +4424,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4238,40 +4448,40 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4287,18 +4497,20 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4323,13 +4535,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4347,7 +4559,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4362,25 +4574,25 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4396,18 +4608,20 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4432,13 +4646,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4456,13 +4670,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4471,52 +4685,54 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4541,13 +4757,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4565,7 +4781,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4580,25 +4796,25 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4614,18 +4830,20 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4650,13 +4868,11 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4674,7 +4890,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4689,25 +4905,25 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4723,20 +4939,18 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>285</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>286</v>
+        <v>174</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4785,7 +4999,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4797,35 +5011,35 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>177</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4837,16 +5051,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>180</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>181</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4884,34 +5098,34 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>183</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>177</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
@@ -4922,10 +5136,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4936,7 +5150,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -4945,21 +5159,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5007,7 +5223,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5022,21 +5238,21 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5044,31 +5260,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>304</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5116,13 +5336,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5131,50 +5351,50 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>222</v>
+        <v>318</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>223</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>224</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5225,10 +5445,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>225</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>87</v>
@@ -5237,24 +5457,24 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>226</v>
+        <v>321</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5262,10 +5482,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5277,13 +5497,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>132</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>133</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>134</v>
+        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5322,62 +5542,62 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5386,13 +5606,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5443,72 +5663,68 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5556,50 +5772,50 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5608,17 +5824,15 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>345</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5643,13 +5857,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5667,7 +5881,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5682,53 +5896,53 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>167</v>
+        <v>352</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5754,13 +5968,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -5778,13 +5992,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -5793,25 +6007,25 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>190</v>
+        <v>356</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5830,16 +6044,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>337</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5889,7 +6103,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5904,7 +6118,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -5915,10 +6129,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5929,7 +6143,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -5941,15 +6155,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>270</v>
+        <v>365</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -5998,13 +6214,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6013,21 +6229,21 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>267</v>
+        <v>369</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6035,13 +6251,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6050,17 +6266,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6085,13 +6299,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6109,13 +6323,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6124,7 +6338,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>209</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6135,10 +6349,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6149,7 +6363,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6161,17 +6375,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>353</v>
+        <v>174</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6196,13 +6408,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6220,7 +6432,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>176</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6232,10 +6444,10 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>177</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6246,10 +6458,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6257,10 +6469,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6272,17 +6484,15 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6319,19 +6529,17 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>359</v>
+        <v>183</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6343,10 +6551,10 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6355,26 +6563,28 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6383,13 +6593,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>379</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>223</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>224</v>
+        <v>381</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6440,22 +6650,22 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6466,14 +6676,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>151</v>
+        <v>383</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6486,24 +6696,26 @@
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>229</v>
+        <v>385</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6539,19 +6751,19 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>386</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6566,7 +6778,7 @@
         <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6577,10 +6789,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6600,19 +6812,19 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>197</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6638,13 +6850,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6662,7 +6874,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6677,52 +6889,54 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -6747,13 +6961,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -6771,13 +6985,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -6786,32 +7000,32 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>376</v>
+        <v>266</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>130</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6820,18 +7034,20 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -6880,10 +7096,10 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>87</v>
@@ -6895,17 +7111,1008 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>130</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM48">
+  <autoFilter ref="A1:AM57">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6915,7 +8122,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1020,7 +1020,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -1106,7 +1106,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -1129,7 +1129,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1768,7 +1768,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="175.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:12:43+00:00</t>
+    <t>2026-10-08T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,7 +273,7 @@
   </si>
   <si>
     <t>ait-1:AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
-ait-2:AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+ait-2:AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allergy-status-combination:Erlaubte Kombinationen von clinicalStatus und verificationStatus: active mit unconfirmed, presumed oder confirmed; resolved mit refuted. {(clinicalStatus.coding.exists(code = 'active') and verificationStatus.coding.exists(code = 'unconfirmed' or code = 'presumed' or code = 'confirmed')) or (clinicalStatus.coding.exists(code = 'resolved') and verificationStatus.coding.exists(code = 'refuted'))}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
@@ -779,7 +779,7 @@
     <t>AllergyIntolerance.clinicalStatus</t>
   </si>
   <si>
-    <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
+    <t>Status der Allergie; mögliche Codes: active | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -789,7 +789,7 @@
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-clinical|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-allergyintolerance-clinical-status-vs</t>
   </si>
   <si>
     <t>ait-1
@@ -805,7 +805,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | confirmed | refuted | entered-in-error.</t>
+    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | presumed | confirmed | refuted.</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -814,10 +814,7 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>Assertion about certainty associated with a propensity, or potential risk, of a reaction to the identified substance.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-verification|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-allergyintolerance-verification-status-vs</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -1783,7 +1780,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.60546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4315,9 +4312,7 @@
       <c r="X23" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y23" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
         <v>248</v>
       </c>
@@ -4426,11 +4421,9 @@
       <c r="X24" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4463,7 +4456,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>251</v>
@@ -4474,14 +4467,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4503,13 +4496,13 @@
         <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4538,11 +4531,11 @@
         <v>190</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4559,7 +4552,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4574,25 +4567,25 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4614,13 +4607,13 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4649,11 +4642,11 @@
         <v>190</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4670,7 +4663,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4685,25 +4678,25 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4725,13 +4718,13 @@
         <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4760,11 +4753,11 @@
         <v>190</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4781,7 +4774,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4796,25 +4789,25 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4836,13 +4829,13 @@
         <v>197</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4872,7 +4865,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4890,7 +4883,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4905,21 +4898,21 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5025,10 +5018,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5136,10 +5129,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5162,19 +5155,19 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5223,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5238,21 +5231,21 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5278,16 +5271,16 @@
         <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5336,7 +5329,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5351,25 +5344,25 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5388,13 +5381,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5445,7 +5438,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -5460,21 +5453,21 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5497,13 +5490,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5554,7 +5547,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5569,10 +5562,10 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5580,10 +5573,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5606,13 +5599,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5663,7 +5656,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5678,10 +5671,10 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5689,10 +5682,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5715,13 +5708,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5772,7 +5765,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5787,25 +5780,25 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5824,13 +5817,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5881,7 +5874,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5896,10 +5889,10 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5907,14 +5900,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5933,16 +5926,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5992,7 +5985,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6007,21 +6000,21 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6044,16 +6037,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6103,7 +6096,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6118,7 +6111,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -6129,10 +6122,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6155,16 +6148,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6214,7 +6207,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6229,7 +6222,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -6240,10 +6233,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6266,13 +6259,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6323,7 +6316,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6338,7 +6331,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6349,10 +6342,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6458,10 +6451,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6565,13 +6558,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
@@ -6593,13 +6586,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6676,14 +6669,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6705,10 +6698,10 @@
         <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>154</v>
@@ -6763,7 +6756,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6789,10 +6782,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6818,13 +6811,13 @@
         <v>197</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6850,14 +6843,14 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Y46" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Y46" t="s" s="2">
+      <c r="Z46" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6874,7 +6867,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6889,7 +6882,7 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6900,14 +6893,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6929,13 +6922,13 @@
         <v>197</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6961,14 +6954,14 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
       </c>
@@ -6985,7 +6978,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>87</v>
@@ -7000,25 +6993,25 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7040,13 +7033,13 @@
         <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7096,7 +7089,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7111,7 +7104,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
@@ -7122,10 +7115,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7148,13 +7141,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7205,7 +7198,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7220,21 +7213,21 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7260,13 +7253,13 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7295,11 +7288,11 @@
         <v>190</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7316,7 +7309,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7331,7 +7324,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -7342,10 +7335,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7371,13 +7364,13 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7403,14 +7396,14 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7427,7 +7420,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7442,7 +7435,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7453,10 +7446,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7479,16 +7472,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7538,7 +7531,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7553,7 +7546,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7564,10 +7557,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7673,10 +7666,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7784,10 +7777,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7810,16 +7803,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7869,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7884,7 +7877,7 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -7895,10 +7888,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7921,13 +7914,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7978,7 +7971,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7993,7 +7986,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -8004,10 +7997,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8030,13 +8023,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8087,7 +8080,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -8102,7 +8095,7 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das AT e-Diagnose AllergyIntolerance-Profil leitet sich vom AllergyIntolerance-Profil ab und passt dieses für die Anforderungen der e-Diagnose an.</t>
+    <t>Dieses AllergyIntolerance-Profil passt die AllergyIntolerance-Resource für die Anforderungen der e-Diagnose an.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -460,7 +460,7 @@
 </t>
   </si>
   <si>
-    <t>AT ELGA Reported (Fremdangabe)</t>
+    <t>True wenn diese Allergie fremdberichtet ist.</t>
   </si>
   <si>
     <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
@@ -480,111 +480,117 @@
 </t>
   </si>
   <si>
-    <t>AT ELGA Entered In Error</t>
+    <t>Dokumentation des GDA der den Eintrag storniert hat.</t>
   </si>
   <si>
     <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
   </si>
   <si>
+    <t>AllergyIntolerance.extension:evidence</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-evidence}
+</t>
+  </si>
+  <si>
+    <t>Verweis auf e-Befunde als medizinische Evidenz.</t>
+  </si>
+  <si>
+    <t>Verweis auf e-Befunde (z. B. Laborbefund, Entlassungsbrief) als medizinische Evidenz, analog zu Condition.evidence.detail.</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.modifierExtension</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>External ids for this item</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>IAM-7</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier</t>
+  </si>
+  <si>
+    <t>businessIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier innerhalb der e-Diagnose für einen Eintrag.</t>
+  </si>
+  <si>
+    <t>Dieser Identifier wird von der Fachanwendung e-Diagnose vergeben, sollte dieser durch den Client nicht gesetzt werden. Ein Client kann diesen Identifier nutzen, um einzelne Einträge im Zuge einer Bearbeitung miteinander zu verknüpfen.</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:businessIdentifier.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier.extension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External ids for this item</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>IAM-7</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier:businessIdentifier</t>
-  </si>
-  <si>
-    <t>businessIdentifier</t>
-  </si>
-  <si>
-    <t>Identifier innerhalb der e-Diagnose für einen Eintrag.</t>
-  </si>
-  <si>
-    <t>Dieser Identifier wird von der Fachanwendung e-Diagnose vergeben, sollte dieser durch den Client nicht gesetzt werden. Ein Client kann diesen Identifier nutzen, um einzelne Einträge im Zuge einer Bearbeitung miteinander zu verknüpfen.</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier:businessIdentifier.id</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier:businessIdentifier.extension</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -827,7 +833,7 @@
 Class</t>
   </si>
   <si>
-    <t>Kennzeichnung, ob es sich um eine Allergie oder Intoleranz handelt.</t>
+    <t>Unterscheidung zwischen Allergie und Intoleranz fachlich oft nicht einfach. Für die e-Diagnose insofern nicht relevant.</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -858,7 +864,7 @@
 TypeReaction TypeClass</t>
   </si>
   <si>
-    <t>ToDo - falls nur med. rele. dann ist es nicht notwendig, fachlich klären: Differenzierung nach Kontext z. B. Medikamente, Lebensmittel oder Umwelt.</t>
+    <t>Unterscheidung zwischen Kategorien wird über den code abgebildet. Für die e-Diagnose insofern nicht relevant.</t>
   </si>
   <si>
     <t>Category of the identified substance.</t>
@@ -886,7 +892,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>Einschätzung des Schweregrads, z. B. im Hinblick auf eine Anaphylaxie.</t>
+    <t>Value-Set mit beschränkter Aussagekraft. Für die e-Diagnose insofern nicht relevant.</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -917,7 +923,7 @@
 </t>
   </si>
   <si>
-    <t>Allergiecode; Freitext ist nicht zulässig.</t>
+    <t>Allergiecode</t>
   </si>
   <si>
     <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -989,7 +995,7 @@
     <t>AllergyIntolerance.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Die ursprüngliche textuelle Eingabe soll im Feld reaction.note.text dokumentiert werden.</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1043,7 +1049,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt.</t>
+    <t>In e-Diagnose werden keine Behandlungskontakte dokumentiert.</t>
   </si>
   <si>
     <t>The encounter when the allergy or intolerance was asserted.</t>
@@ -1062,7 +1068,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>Erstes Aufzeichnungsdatum der Allergie bzw. Allergiesymptomatik.</t>
+    <t>Für e-Diagnose ist insbesondere der Beginn der Reaktion relevant.</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -1081,7 +1087,7 @@
 </t>
   </si>
   <si>
-    <t>Dokumentationsdatum.</t>
+    <t>Dokumentationsdatum</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -1107,7 +1113,7 @@
 </t>
   </si>
   <si>
-    <t>GDA, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
+    <t>GDA, der die Allergie in der e-Diagnose erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -1151,7 +1157,7 @@
     <t>AllergyIntolerance.lastOccurrence</t>
   </si>
   <si>
-    <t>Letztes Auftreten der Symptomatik; siehe Manifestation.</t>
+    <t>Es wird nur eine Reaktion dokumentiert, weshalb dieses Datum gleichbedeutend mit reaction.onset ist.</t>
   </si>
   <si>
     <t>Represents the date and/or time of the last known occurrence of a reaction event.</t>
@@ -1170,7 +1176,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen; Freitext wird in reaction beschrieben.</t>
+    <t>Weitere textuelle Eingaben sollen im Feld reaction.note.text dokumentiert werden.</t>
   </si>
   <si>
     <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
@@ -1223,24 +1229,13 @@
     <t>AllergyIntolerance.reaction.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
-    <t>Spezifische Substanz, die zur Allergie führt; wird über AllergyIntolerance.code abgebildet.</t>
+    <t>Wird über code abgebildet.</t>
   </si>
   <si>
     <t>Identification of the specific substance (or pharmaceutical product) considered to be responsible for the Adverse Reaction event. Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -1277,10 +1272,7 @@
     <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-condition-code</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1293,9 +1285,6 @@
 Text</t>
   </si>
   <si>
-    <t>Textbasierte Zusammenfassung der allergischen Reaktion.</t>
-  </si>
-  <si>
     <t>Text description about the reaction as a whole, including details of the manifestation if required.</t>
   </si>
   <si>
@@ -1320,7 +1309,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>Schweregrad der Reaktion, z. B. mild oder moderat.</t>
+    <t>mild | moderate | severe (of event as a whole)</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -1338,7 +1327,7 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>Art der Exposition der betroffenen Person gegenüber der Substanz.</t>
+    <t>How the subject was exposed to the substance</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.</t>
@@ -1381,7 +1370,7 @@
 string</t>
   </si>
   <si>
-    <t>Individual responsible for the annotation</t>
+    <t>Wird über recorder abgebildet.</t>
   </si>
   <si>
     <t>The individual responsible for making the annotation.</t>
@@ -1399,7 +1388,7 @@
     <t>AllergyIntolerance.reaction.note.time</t>
   </si>
   <si>
-    <t>When the annotation was made</t>
+    <t>Wird über recordedDate abgebildet.</t>
   </si>
   <si>
     <t>Indicates when this particular annotation was made.</t>
@@ -1422,6 +1411,9 @@
   </si>
   <si>
     <t>The text of the annotation in markdown format.</t>
+  </si>
+  <si>
+    <t>500</t>
   </si>
   <si>
     <t>Annotation.text</t>
@@ -1752,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.46484375" customWidth="true" bestFit="true"/>
@@ -1769,7 +1761,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -2261,7 +2253,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -2796,7 +2788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2817,7 +2809,7 @@
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
@@ -2907,7 +2899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2928,7 +2920,7 @@
         <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3018,16 +3010,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3037,29 +3031,25 @@
         <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3107,7 +3097,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3116,13 +3106,13 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>21</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3147,32 +3137,28 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3208,17 +3194,19 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3230,28 +3218,26 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="C14" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3260,10 +3246,10 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3275,10 +3261,10 @@
         <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>161</v>
@@ -3321,16 +3307,14 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>157</v>
@@ -3357,14 +3341,16 @@
         <v>166</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3376,25 +3362,29 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3442,47 +3432,47 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3494,17 +3484,15 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3541,31 +3529,31 @@
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>177</v>
@@ -3579,46 +3567,44 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3642,60 +3628,60 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3706,31 +3692,31 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3755,13 +3741,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3779,7 +3765,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3794,21 +3780,21 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3816,7 +3802,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
@@ -3831,19 +3817,19 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3853,10 +3839,10 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3868,13 +3854,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3892,7 +3878,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3907,21 +3893,21 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3935,7 +3921,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -3944,18 +3930,20 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3964,10 +3952,10 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -4003,7 +3991,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4018,21 +4006,21 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4040,13 +4028,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -4055,15 +4043,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4076,7 +4066,7 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>21</v>
@@ -4112,7 +4102,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4127,21 +4117,21 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4164,17 +4154,15 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4223,7 +4211,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4238,21 +4226,21 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4260,31 +4248,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4310,11 +4298,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4332,7 +4322,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4341,27 +4331,27 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4384,16 +4374,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4419,11 +4409,11 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4441,7 +4431,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4450,59 +4440,59 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4528,13 +4518,11 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4552,7 +4540,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4561,31 +4549,31 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4607,13 +4595,13 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4639,13 +4627,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4663,13 +4651,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4678,25 +4666,25 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4718,13 +4706,13 @@
         <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4750,13 +4738,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4774,13 +4762,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -4789,35 +4777,35 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4826,16 +4814,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4861,11 +4849,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4883,7 +4873,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4898,52 +4888,54 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4968,13 +4960,11 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4992,7 +4982,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>176</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5004,35 +4994,35 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5044,17 +5034,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5091,31 +5079,31 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>177</v>
@@ -5129,14 +5117,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5152,23 +5140,21 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>181</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5204,19 +5190,19 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5228,24 +5214,24 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>305</v>
+        <v>177</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5256,7 +5242,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5268,19 +5254,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5329,13 +5315,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5344,35 +5330,35 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5381,16 +5367,20 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5438,10 +5428,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>87</v>
@@ -5453,50 +5443,50 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5547,10 +5537,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>87</v>
@@ -5562,21 +5552,21 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5599,13 +5589,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5656,7 +5646,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5671,21 +5661,21 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5693,13 +5683,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5708,13 +5698,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5765,7 +5755,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5780,25 +5770,25 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5817,13 +5807,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5874,7 +5864,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5889,54 +5879,52 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5985,7 +5973,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6000,53 +5988,53 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6096,7 +6084,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6111,21 +6099,21 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6148,16 +6136,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6207,13 +6195,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6222,7 +6210,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -6231,12 +6219,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6244,13 +6232,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6259,15 +6247,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6316,7 +6306,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6331,7 +6321,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6340,12 +6330,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6353,13 +6343,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6368,13 +6358,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>173</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>174</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6425,22 +6415,22 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>177</v>
+        <v>375</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6451,10 +6441,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6462,11 +6452,11 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6477,13 +6467,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6522,32 +6512,34 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6556,16 +6548,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C44" t="s" s="2">
         <v>377</v>
       </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6574,10 +6564,10 @@
         <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6586,13 +6576,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>133</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
+        <v>134</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6631,19 +6621,17 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6652,7 +6640,7 @@
         <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>138</v>
@@ -6667,48 +6655,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>380</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6756,7 +6742,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>385</v>
+        <v>185</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6765,13 +6751,13 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6782,10 +6768,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6802,23 +6788,21 @@
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>133</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6843,13 +6827,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6867,22 +6851,22 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6891,26 +6875,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -6919,16 +6903,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6954,13 +6938,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Y47" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="Z47" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -6978,13 +6962,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -6993,35 +6977,35 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>265</v>
+        <v>392</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7030,16 +7014,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7065,13 +7049,11 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7089,13 +7071,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7104,32 +7086,32 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>407</v>
+        <v>267</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7141,15 +7123,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>336</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7198,7 +7182,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7213,21 +7197,21 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>333</v>
+        <v>404</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7238,10 +7222,10 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7250,17 +7234,15 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>338</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7285,13 +7267,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7309,7 +7291,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7324,21 +7306,21 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7349,7 +7331,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7361,16 +7343,16 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7396,13 +7378,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>390</v>
+        <v>192</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7420,7 +7402,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7435,7 +7417,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>424</v>
+        <v>286</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7446,10 +7428,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7472,16 +7454,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>364</v>
+        <v>199</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7507,13 +7489,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7531,13 +7513,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7546,7 +7528,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7555,12 +7537,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7574,7 +7556,7 @@
         <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -7583,15 +7565,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>366</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>174</v>
+        <v>423</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7640,22 +7624,22 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>176</v>
+        <v>422</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>177</v>
+        <v>370</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7666,21 +7650,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7692,17 +7676,15 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7739,31 +7721,31 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>177</v>
@@ -7777,21 +7759,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7800,19 +7782,19 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>432</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>181</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>182</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>183</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7850,48 +7832,48 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>185</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>437</v>
+        <v>177</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7914,15 +7896,17 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -7971,7 +7955,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7986,7 +7970,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -7997,10 +7981,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8008,10 +7992,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8023,13 +8007,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>444</v>
+        <v>338</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8080,10 +8064,10 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>87</v>
@@ -8095,7 +8079,7 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -8104,8 +8088,117 @@
         <v>130</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM57">
+  <autoFilter ref="A1:AM58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8115,7 +8208,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
